--- a/output/upload/S00026_2244_케어백간병플러스보험_무배당.xlsx
+++ b/output/upload/S00026_2244_케어백간병플러스보험_무배당.xlsx
@@ -1304,17 +1304,9 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="6" t="inlineStr">
@@ -1398,17 +1390,9 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="D8" s="5" t="inlineStr"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="6" t="inlineStr">
@@ -1492,17 +1476,9 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
+      <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="D9" s="5" t="inlineStr"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="6" t="inlineStr">
@@ -1586,17 +1562,9 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="D10" s="5" t="inlineStr"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="6" t="inlineStr">
@@ -1680,17 +1648,9 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
+      <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="D11" s="5" t="inlineStr"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="6" t="inlineStr">
@@ -1774,17 +1734,9 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
+      <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="D12" s="5" t="inlineStr"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="6" t="inlineStr">
@@ -1868,17 +1820,9 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
+      <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="D13" s="5" t="inlineStr"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="6" t="inlineStr">
@@ -1962,17 +1906,9 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
+      <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="D14" s="5" t="inlineStr"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="6" t="inlineStr">
@@ -2056,17 +1992,9 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
+      <c r="B15" s="5" t="inlineStr"/>
       <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="D15" s="5" t="inlineStr"/>
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
       <c r="G15" s="6" t="inlineStr">
@@ -2150,17 +2078,9 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
+      <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="D16" s="5" t="inlineStr"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
       <c r="G16" s="6" t="inlineStr">
@@ -2244,17 +2164,9 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
+      <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="D17" s="5" t="inlineStr"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="6" t="inlineStr">
@@ -2338,17 +2250,9 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
+      <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="6" t="inlineStr">
@@ -2432,17 +2336,9 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
+      <c r="B19" s="5" t="inlineStr"/>
       <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="D19" s="5" t="inlineStr"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
       <c r="G19" s="6" t="inlineStr">
@@ -2526,17 +2422,9 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
+      <c r="B20" s="5" t="inlineStr"/>
       <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="D20" s="5" t="inlineStr"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
       <c r="G20" s="6" t="inlineStr">
@@ -2620,17 +2508,9 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
+      <c r="B21" s="5" t="inlineStr"/>
       <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="D21" s="5" t="inlineStr"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
       <c r="G21" s="6" t="inlineStr">
@@ -2714,17 +2594,9 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
+      <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="D22" s="5" t="inlineStr"/>
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="6" t="inlineStr">
@@ -2807,16 +2679,8 @@
       <c r="AV22" s="6" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2867,16 +2731,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2927,16 +2783,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2987,16 +2835,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3047,16 +2887,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3107,16 +2939,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3167,16 +2991,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3227,16 +3043,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3287,16 +3095,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3347,16 +3147,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3407,16 +3199,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3467,16 +3251,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3527,16 +3303,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3587,16 +3355,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3647,16 +3407,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3707,16 +3459,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3767,16 +3511,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3827,16 +3563,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3887,16 +3615,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3947,16 +3667,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4007,16 +3719,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4067,16 +3771,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4127,16 +3823,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4187,16 +3875,8 @@
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4247,16 +3927,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4307,16 +3979,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4367,16 +4031,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4427,16 +4083,8 @@
       </c>
     </row>
     <row r="50">
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4487,16 +4135,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4547,16 +4187,8 @@
       </c>
     </row>
     <row r="52">
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4607,16 +4239,8 @@
       </c>
     </row>
     <row r="53">
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4667,16 +4291,8 @@
       </c>
     </row>
     <row r="54">
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4727,16 +4343,8 @@
       </c>
     </row>
     <row r="55">
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4787,16 +4395,8 @@
       </c>
     </row>
     <row r="56">
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4847,16 +4447,8 @@
       </c>
     </row>
     <row r="57">
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4907,16 +4499,8 @@
       </c>
     </row>
     <row r="58">
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4967,16 +4551,8 @@
       </c>
     </row>
     <row r="59">
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5027,16 +4603,8 @@
       </c>
     </row>
     <row r="60">
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5087,16 +4655,8 @@
       </c>
     </row>
     <row r="61">
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5147,16 +4707,8 @@
       </c>
     </row>
     <row r="62">
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5207,16 +4759,8 @@
       </c>
     </row>
     <row r="63">
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5267,16 +4811,8 @@
       </c>
     </row>
     <row r="64">
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5327,16 +4863,8 @@
       </c>
     </row>
     <row r="65">
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5387,16 +4915,8 @@
       </c>
     </row>
     <row r="66">
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5447,16 +4967,8 @@
       </c>
     </row>
     <row r="67">
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5507,16 +5019,8 @@
       </c>
     </row>
     <row r="68">
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5567,16 +5071,8 @@
       </c>
     </row>
     <row r="69">
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5627,16 +5123,8 @@
       </c>
     </row>
     <row r="70">
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5687,16 +5175,8 @@
       </c>
     </row>
     <row r="71">
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5747,16 +5227,8 @@
       </c>
     </row>
     <row r="72">
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5807,16 +5279,8 @@
       </c>
     </row>
     <row r="73">
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5867,16 +5331,8 @@
       </c>
     </row>
     <row r="74">
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5927,16 +5383,8 @@
       </c>
     </row>
     <row r="75">
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5987,16 +5435,8 @@
       </c>
     </row>
     <row r="76">
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6047,16 +5487,8 @@
       </c>
     </row>
     <row r="77">
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6107,16 +5539,8 @@
       </c>
     </row>
     <row r="78">
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6167,16 +5591,8 @@
       </c>
     </row>
     <row r="79">
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6227,16 +5643,8 @@
       </c>
     </row>
     <row r="80">
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6287,16 +5695,8 @@
       </c>
     </row>
     <row r="81">
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6347,16 +5747,8 @@
       </c>
     </row>
     <row r="82">
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6407,16 +5799,8 @@
       </c>
     </row>
     <row r="83">
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6467,16 +5851,8 @@
       </c>
     </row>
     <row r="84">
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6527,16 +5903,8 @@
       </c>
     </row>
     <row r="85">
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6587,16 +5955,8 @@
       </c>
     </row>
     <row r="86">
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6647,16 +6007,8 @@
       </c>
     </row>
     <row r="87">
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6707,16 +6059,8 @@
       </c>
     </row>
     <row r="88">
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6767,16 +6111,8 @@
       </c>
     </row>
     <row r="89">
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6827,16 +6163,8 @@
       </c>
     </row>
     <row r="90">
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6887,16 +6215,8 @@
       </c>
     </row>
     <row r="91">
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6947,16 +6267,8 @@
       </c>
     </row>
     <row r="92">
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7007,16 +6319,8 @@
       </c>
     </row>
     <row r="93">
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7067,16 +6371,8 @@
       </c>
     </row>
     <row r="94">
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7127,16 +6423,8 @@
       </c>
     </row>
     <row r="95">
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7187,16 +6475,8 @@
       </c>
     </row>
     <row r="96">
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7247,16 +6527,8 @@
       </c>
     </row>
     <row r="97">
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7307,16 +6579,8 @@
       </c>
     </row>
     <row r="98">
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7367,16 +6631,8 @@
       </c>
     </row>
     <row r="99">
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7427,16 +6683,8 @@
       </c>
     </row>
     <row r="100">
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7487,16 +6735,8 @@
       </c>
     </row>
     <row r="101">
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7547,16 +6787,8 @@
       </c>
     </row>
     <row r="102">
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7607,16 +6839,8 @@
       </c>
     </row>
     <row r="103">
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7667,16 +6891,8 @@
       </c>
     </row>
     <row r="104">
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7727,16 +6943,8 @@
       </c>
     </row>
     <row r="105">
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7787,16 +6995,8 @@
       </c>
     </row>
     <row r="106">
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7847,16 +7047,8 @@
       </c>
     </row>
     <row r="107">
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7907,16 +7099,8 @@
       </c>
     </row>
     <row r="108">
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7967,16 +7151,8 @@
       </c>
     </row>
     <row r="109">
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -8027,16 +7203,8 @@
       </c>
     </row>
     <row r="110">
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -8087,16 +7255,8 @@
       </c>
     </row>
     <row r="111">
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -8147,16 +7307,8 @@
       </c>
     </row>
     <row r="112">
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -8207,16 +7359,8 @@
       </c>
     </row>
     <row r="113">
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -8267,16 +7411,8 @@
       </c>
     </row>
     <row r="114">
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -8327,16 +7463,8 @@
       </c>
     </row>
     <row r="115">
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -8387,16 +7515,8 @@
       </c>
     </row>
     <row r="116">
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -8447,16 +7567,8 @@
       </c>
     </row>
     <row r="117">
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -8507,16 +7619,8 @@
       </c>
     </row>
     <row r="118">
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -8567,16 +7671,8 @@
       </c>
     </row>
     <row r="119">
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -8627,16 +7723,8 @@
       </c>
     </row>
     <row r="120">
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -8687,16 +7775,8 @@
       </c>
     </row>
     <row r="121">
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -8747,16 +7827,8 @@
       </c>
     </row>
     <row r="122">
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -8807,16 +7879,8 @@
       </c>
     </row>
     <row r="123">
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="D123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -8867,16 +7931,8 @@
       </c>
     </row>
     <row r="124">
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -8927,16 +7983,8 @@
       </c>
     </row>
     <row r="125">
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -8987,16 +8035,8 @@
       </c>
     </row>
     <row r="126">
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>2244A01</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>7781006</t>
-        </is>
-      </c>
+      <c r="B126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00026_2244_케어백간병플러스보험_무배당.xlsx
+++ b/output/upload/S00026_2244_케어백간병플러스보험_무배당.xlsx
@@ -1304,11 +1304,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1390,11 +1410,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1476,11 +1516,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1562,11 +1622,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1648,11 +1728,31 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1734,11 +1834,31 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1820,11 +1940,31 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1906,11 +2046,31 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1992,11 +2152,31 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2078,11 +2258,31 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2164,11 +2364,31 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2250,11 +2470,31 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2336,11 +2576,31 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2422,11 +2682,31 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="inlineStr"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2508,11 +2788,31 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2594,11 +2894,31 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="inlineStr"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2679,8 +2999,31 @@
       <c r="AV22" s="6" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2731,8 +3074,31 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2783,8 +3149,31 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2835,8 +3224,31 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2887,8 +3299,31 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2939,8 +3374,31 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2991,8 +3449,31 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3043,8 +3524,31 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3095,8 +3599,31 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3147,8 +3674,31 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3199,8 +3749,31 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3251,8 +3824,31 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3303,8 +3899,31 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3355,8 +3974,31 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3407,8 +4049,31 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3459,8 +4124,31 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3511,8 +4199,31 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3563,8 +4274,31 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3615,8 +4349,31 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3667,8 +4424,31 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3719,8 +4499,31 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3771,8 +4574,31 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3823,8 +4649,31 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3875,8 +4724,31 @@
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3927,8 +4799,31 @@
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3979,8 +4874,31 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4031,8 +4949,31 @@
       </c>
     </row>
     <row r="49">
-      <c r="B49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4083,8 +5024,31 @@
       </c>
     </row>
     <row r="50">
-      <c r="B50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4135,8 +5099,31 @@
       </c>
     </row>
     <row r="51">
-      <c r="B51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4187,8 +5174,31 @@
       </c>
     </row>
     <row r="52">
-      <c r="B52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4239,8 +5249,31 @@
       </c>
     </row>
     <row r="53">
-      <c r="B53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4291,8 +5324,31 @@
       </c>
     </row>
     <row r="54">
-      <c r="B54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4343,8 +5399,31 @@
       </c>
     </row>
     <row r="55">
-      <c r="B55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4395,8 +5474,31 @@
       </c>
     </row>
     <row r="56">
-      <c r="B56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4447,8 +5549,31 @@
       </c>
     </row>
     <row r="57">
-      <c r="B57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4499,8 +5624,31 @@
       </c>
     </row>
     <row r="58">
-      <c r="B58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4551,8 +5699,31 @@
       </c>
     </row>
     <row r="59">
-      <c r="B59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4603,8 +5774,31 @@
       </c>
     </row>
     <row r="60">
-      <c r="B60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4655,8 +5849,31 @@
       </c>
     </row>
     <row r="61">
-      <c r="B61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4707,8 +5924,31 @@
       </c>
     </row>
     <row r="62">
-      <c r="B62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4759,8 +5999,31 @@
       </c>
     </row>
     <row r="63">
-      <c r="B63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4811,8 +6074,31 @@
       </c>
     </row>
     <row r="64">
-      <c r="B64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4863,8 +6149,31 @@
       </c>
     </row>
     <row r="65">
-      <c r="B65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4915,8 +6224,31 @@
       </c>
     </row>
     <row r="66">
-      <c r="B66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4967,8 +6299,31 @@
       </c>
     </row>
     <row r="67">
-      <c r="B67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5019,8 +6374,31 @@
       </c>
     </row>
     <row r="68">
-      <c r="B68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5071,8 +6449,31 @@
       </c>
     </row>
     <row r="69">
-      <c r="B69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5123,8 +6524,31 @@
       </c>
     </row>
     <row r="70">
-      <c r="B70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5175,8 +6599,31 @@
       </c>
     </row>
     <row r="71">
-      <c r="B71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5227,8 +6674,31 @@
       </c>
     </row>
     <row r="72">
-      <c r="B72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5279,8 +6749,31 @@
       </c>
     </row>
     <row r="73">
-      <c r="B73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5331,8 +6824,31 @@
       </c>
     </row>
     <row r="74">
-      <c r="B74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5383,8 +6899,31 @@
       </c>
     </row>
     <row r="75">
-      <c r="B75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5435,8 +6974,31 @@
       </c>
     </row>
     <row r="76">
-      <c r="B76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5487,8 +7049,31 @@
       </c>
     </row>
     <row r="77">
-      <c r="B77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5539,8 +7124,31 @@
       </c>
     </row>
     <row r="78">
-      <c r="B78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5591,8 +7199,31 @@
       </c>
     </row>
     <row r="79">
-      <c r="B79" t="inlineStr"/>
-      <c r="D79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5643,8 +7274,31 @@
       </c>
     </row>
     <row r="80">
-      <c r="B80" t="inlineStr"/>
-      <c r="D80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5695,8 +7349,31 @@
       </c>
     </row>
     <row r="81">
-      <c r="B81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5747,8 +7424,31 @@
       </c>
     </row>
     <row r="82">
-      <c r="B82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5799,8 +7499,31 @@
       </c>
     </row>
     <row r="83">
-      <c r="B83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G83" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5851,8 +7574,31 @@
       </c>
     </row>
     <row r="84">
-      <c r="B84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G84" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5903,8 +7649,31 @@
       </c>
     </row>
     <row r="85">
-      <c r="B85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5955,8 +7724,31 @@
       </c>
     </row>
     <row r="86">
-      <c r="B86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G86" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6007,8 +7799,31 @@
       </c>
     </row>
     <row r="87">
-      <c r="B87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6059,8 +7874,31 @@
       </c>
     </row>
     <row r="88">
-      <c r="B88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6111,8 +7949,31 @@
       </c>
     </row>
     <row r="89">
-      <c r="B89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6163,8 +8024,31 @@
       </c>
     </row>
     <row r="90">
-      <c r="B90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6215,8 +8099,31 @@
       </c>
     </row>
     <row r="91">
-      <c r="B91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6267,8 +8174,31 @@
       </c>
     </row>
     <row r="92">
-      <c r="B92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6319,8 +8249,31 @@
       </c>
     </row>
     <row r="93">
-      <c r="B93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G93" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6371,8 +8324,31 @@
       </c>
     </row>
     <row r="94">
-      <c r="B94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G94" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6423,8 +8399,31 @@
       </c>
     </row>
     <row r="95">
-      <c r="B95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G95" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6475,8 +8474,31 @@
       </c>
     </row>
     <row r="96">
-      <c r="B96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G96" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6527,8 +8549,31 @@
       </c>
     </row>
     <row r="97">
-      <c r="B97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G97" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6579,8 +8624,31 @@
       </c>
     </row>
     <row r="98">
-      <c r="B98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G98" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6631,8 +8699,31 @@
       </c>
     </row>
     <row r="99">
-      <c r="B99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G99" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6683,8 +8774,31 @@
       </c>
     </row>
     <row r="100">
-      <c r="B100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G100" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6735,8 +8849,31 @@
       </c>
     </row>
     <row r="101">
-      <c r="B101" t="inlineStr"/>
-      <c r="D101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G101" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6787,8 +8924,31 @@
       </c>
     </row>
     <row r="102">
-      <c r="B102" t="inlineStr"/>
-      <c r="D102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G102" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6839,8 +8999,31 @@
       </c>
     </row>
     <row r="103">
-      <c r="B103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G103" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6891,8 +9074,31 @@
       </c>
     </row>
     <row r="104">
-      <c r="B104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G104" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6943,8 +9149,31 @@
       </c>
     </row>
     <row r="105">
-      <c r="B105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G105" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -6995,8 +9224,31 @@
       </c>
     </row>
     <row r="106">
-      <c r="B106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G106" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7047,8 +9299,31 @@
       </c>
     </row>
     <row r="107">
-      <c r="B107" t="inlineStr"/>
-      <c r="D107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G107" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7099,8 +9374,31 @@
       </c>
     </row>
     <row r="108">
-      <c r="B108" t="inlineStr"/>
-      <c r="D108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G108" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7151,8 +9449,31 @@
       </c>
     </row>
     <row r="109">
-      <c r="B109" t="inlineStr"/>
-      <c r="D109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G109" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7203,8 +9524,31 @@
       </c>
     </row>
     <row r="110">
-      <c r="B110" t="inlineStr"/>
-      <c r="D110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G110" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7255,8 +9599,31 @@
       </c>
     </row>
     <row r="111">
-      <c r="B111" t="inlineStr"/>
-      <c r="D111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G111" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7307,8 +9674,31 @@
       </c>
     </row>
     <row r="112">
-      <c r="B112" t="inlineStr"/>
-      <c r="D112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G112" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7359,8 +9749,31 @@
       </c>
     </row>
     <row r="113">
-      <c r="B113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G113" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7411,8 +9824,31 @@
       </c>
     </row>
     <row r="114">
-      <c r="B114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G114" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7463,8 +9899,31 @@
       </c>
     </row>
     <row r="115">
-      <c r="B115" t="inlineStr"/>
-      <c r="D115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G115" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7515,8 +9974,31 @@
       </c>
     </row>
     <row r="116">
-      <c r="B116" t="inlineStr"/>
-      <c r="D116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G116" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7567,8 +10049,31 @@
       </c>
     </row>
     <row r="117">
-      <c r="B117" t="inlineStr"/>
-      <c r="D117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G117" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7619,8 +10124,31 @@
       </c>
     </row>
     <row r="118">
-      <c r="B118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G118" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7671,8 +10199,31 @@
       </c>
     </row>
     <row r="119">
-      <c r="B119" t="inlineStr"/>
-      <c r="D119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G119" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7723,8 +10274,31 @@
       </c>
     </row>
     <row r="120">
-      <c r="B120" t="inlineStr"/>
-      <c r="D120" t="inlineStr"/>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G120" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7775,8 +10349,31 @@
       </c>
     </row>
     <row r="121">
-      <c r="B121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G121" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7827,8 +10424,31 @@
       </c>
     </row>
     <row r="122">
-      <c r="B122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G122" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7879,8 +10499,31 @@
       </c>
     </row>
     <row r="123">
-      <c r="B123" t="inlineStr"/>
-      <c r="D123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G123" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7931,8 +10574,31 @@
       </c>
     </row>
     <row r="124">
-      <c r="B124" t="inlineStr"/>
-      <c r="D124" t="inlineStr"/>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G124" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -7983,8 +10649,31 @@
       </c>
     </row>
     <row r="125">
-      <c r="B125" t="inlineStr"/>
-      <c r="D125" t="inlineStr"/>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G125" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -8035,8 +10724,31 @@
       </c>
     </row>
     <row r="126">
-      <c r="B126" t="inlineStr"/>
-      <c r="D126" t="inlineStr"/>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2244A01</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>22441</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>한화생명 케어백간병플러스보험 무배당 간편가입형(0년) 해약환급금 일부지급형(납입기간중 50%, 납입기간후 100%)</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G126" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00026_2244_케어백간병플러스보험_무배당.xlsx
+++ b/output/upload/S00026_2244_케어백간병플러스보험_무배당.xlsx
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6686,7 +6686,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -9536,7 +9536,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9611,7 +9611,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -9686,7 +9686,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -9761,7 +9761,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -10511,7 +10511,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -10661,7 +10661,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>22441</t>
+          <t>2244001</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
